--- a/public/PresupuestoInicial/Poliza Inicial v2.xlsx
+++ b/public/PresupuestoInicial/Poliza Inicial v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflores\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SAC-IPE\public\PresupuestoInicial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE430C65-1D1F-41EB-847B-1B6A4B85A38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C446ADD-711D-4A31-B171-39728BC7A075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="990" windowWidth="21375" windowHeight="15450" tabRatio="840" xr2:uid="{1ABF5C7F-72DD-4BD5-835F-CAF0BF8EAFC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" xr2:uid="{1ABF5C7F-72DD-4BD5-835F-CAF0BF8EAFC5}"/>
   </bookViews>
   <sheets>
     <sheet name="POLIZA PRUEBA TECNOLOGIAS" sheetId="17" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="269">
   <si>
     <t>Cuenta</t>
   </si>
@@ -288,16 +288,10 @@
     <t>Instituto Mexicano del Seguro Social (IMSS)</t>
   </si>
   <si>
-    <t>Aportaciones para seguros</t>
-  </si>
-  <si>
     <t>2.1.1.1.01.03</t>
   </si>
   <si>
     <t>2.1.1.1.04.01</t>
-  </si>
-  <si>
-    <t>2.1.1.1.04.10</t>
   </si>
   <si>
     <t>1.1.1.2.01.03</t>
@@ -950,22 +944,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1296,13 +1287,14 @@
   <sheetPr>
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="76.28515625" customWidth="1"/>
     <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1313,13 +1305,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1327,29 +1319,27 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3">
         <v>10427702.550000001</v>
       </c>
-      <c r="D2" s="4"/>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3">
         <v>5030912.280000153</v>
       </c>
-      <c r="D3" s="4"/>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1362,9 +1352,8 @@
       <c r="C4" s="3">
         <v>63757879.170000002</v>
       </c>
-      <c r="D4" s="4"/>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1377,99 +1366,92 @@
       <c r="C5" s="3">
         <v>389222225.61000001</v>
       </c>
-      <c r="D5" s="4"/>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
       </c>
       <c r="C6" s="3">
         <v>12159040.85</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
         <v>90</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
       </c>
       <c r="C7" s="3">
         <v>1921264.28</v>
       </c>
-      <c r="D7" s="4"/>
       <c r="E7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
         <v>100</v>
-      </c>
-      <c r="B8" t="s">
-        <v>102</v>
       </c>
       <c r="C8" s="3">
         <v>486392.64</v>
       </c>
-      <c r="D8" s="4"/>
       <c r="E8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
         <v>101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
       </c>
       <c r="C9" s="3">
         <v>4789717.675999999</v>
       </c>
-      <c r="D9" s="4"/>
       <c r="E9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
         <v>104</v>
-      </c>
-      <c r="B10" t="s">
-        <v>106</v>
       </c>
       <c r="C10" s="3">
         <v>2859908.75</v>
       </c>
-      <c r="D10" s="4"/>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
         <v>105</v>
-      </c>
-      <c r="B11" t="s">
-        <v>107</v>
       </c>
       <c r="C11" s="3">
         <v>408287.38000000047</v>
       </c>
-      <c r="D11" s="4"/>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1482,39 +1464,36 @@
       <c r="C12" s="3">
         <v>7259171.2219999693</v>
       </c>
-      <c r="D12" s="4"/>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
         <v>93</v>
-      </c>
-      <c r="B13" t="s">
-        <v>95</v>
       </c>
       <c r="C13" s="3">
         <v>5824449.4800000004</v>
       </c>
-      <c r="D13" s="4"/>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
         <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
       </c>
       <c r="C14" s="3">
         <v>3902927.77</v>
       </c>
-      <c r="D14" s="4"/>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1527,9 +1506,8 @@
       <c r="C15" s="3">
         <v>130865469.68000008</v>
       </c>
-      <c r="D15" s="4"/>
       <c r="E15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1542,9 +1520,8 @@
       <c r="C16" s="3">
         <v>1001566753.15</v>
       </c>
-      <c r="D16" s="4"/>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1552,44 +1529,41 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3">
         <v>3614208.88</v>
       </c>
-      <c r="D17" s="4"/>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" t="s">
         <v>97</v>
-      </c>
-      <c r="B18" t="s">
-        <v>99</v>
       </c>
       <c r="C18" s="3">
         <v>14819806.470000001</v>
       </c>
-      <c r="D18" s="4"/>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3">
         <v>8139.1500000000005</v>
       </c>
-      <c r="D19" s="4"/>
       <c r="E19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1602,144 +1576,134 @@
       <c r="C20" s="3">
         <v>159422573.90000001</v>
       </c>
-      <c r="D20" s="4"/>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="5">
+        <v>174</v>
+      </c>
+      <c r="C21" s="4">
         <v>19707.11</v>
       </c>
-      <c r="D21" s="4"/>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="5">
+        <v>145</v>
+      </c>
+      <c r="C22" s="4">
         <v>12067744.582</v>
       </c>
-      <c r="D22" s="4"/>
       <c r="E22" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="5">
+        <v>147</v>
+      </c>
+      <c r="C23" s="4">
         <v>7887312620.8100004</v>
       </c>
-      <c r="D23" s="4"/>
       <c r="E23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
-      </c>
-      <c r="C24" s="5">
+        <v>149</v>
+      </c>
+      <c r="C24" s="4">
         <v>9846912.7200000007</v>
       </c>
-      <c r="D24" s="4"/>
       <c r="E24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
-      </c>
-      <c r="C25" s="5">
+        <v>168</v>
+      </c>
+      <c r="C25" s="4">
         <v>78720102.680000007</v>
       </c>
-      <c r="D25" s="4"/>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="5">
+        <v>167</v>
+      </c>
+      <c r="C26" s="4">
         <v>90881597.090000004</v>
       </c>
-      <c r="D26" s="4"/>
       <c r="E26" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="5">
+        <v>170</v>
+      </c>
+      <c r="C27" s="4">
         <v>193318.75</v>
       </c>
-      <c r="D27" s="4"/>
       <c r="E27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="5">
+        <v>176</v>
+      </c>
+      <c r="C28" s="4">
         <v>66185.23000000001</v>
       </c>
-      <c r="D28" s="4"/>
       <c r="E28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29" s="5">
+        <v>179</v>
+      </c>
+      <c r="C29" s="4">
         <v>4511698.4800000004</v>
       </c>
-      <c r="D29" s="4"/>
       <c r="E29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1749,42 +1713,39 @@
       <c r="B30" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>476899054.50999999</v>
       </c>
-      <c r="D30" s="4"/>
       <c r="E30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4">
         <v>112480003.84</v>
       </c>
-      <c r="D31" s="4"/>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="5">
+        <v>136</v>
+      </c>
+      <c r="C32" s="4">
         <v>265818246.87500003</v>
       </c>
-      <c r="D32" s="4"/>
       <c r="E32" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1794,12 +1755,11 @@
       <c r="B33" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>615911.88406816381</v>
       </c>
-      <c r="D33" s="4"/>
       <c r="E33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1809,12 +1769,11 @@
       <c r="B34" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>2556343.3448425638</v>
       </c>
-      <c r="D34" s="4"/>
       <c r="E34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1824,12 +1783,11 @@
       <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>34801.649000000012</v>
       </c>
-      <c r="D35" s="4"/>
       <c r="E35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1839,12 +1797,11 @@
       <c r="B36" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>1059043.9312546314</v>
       </c>
-      <c r="D36" s="4"/>
       <c r="E36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1854,12 +1811,11 @@
       <c r="B37" t="s">
         <v>26</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>137240.76</v>
       </c>
-      <c r="D37" s="4"/>
       <c r="E37" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1869,12 +1825,11 @@
       <c r="B38" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>98906.146800000002</v>
       </c>
-      <c r="D38" s="4"/>
       <c r="E38" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,12 +1839,11 @@
       <c r="B39" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>1211367.5394236788</v>
       </c>
-      <c r="D39" s="4"/>
       <c r="E39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1899,12 +1853,11 @@
       <c r="B40" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>1027144.490864502</v>
       </c>
-      <c r="D40" s="4"/>
       <c r="E40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1914,12 +1867,11 @@
       <c r="B41" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>181504.81520000001</v>
       </c>
-      <c r="D41" s="4"/>
       <c r="E41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1929,12 +1881,11 @@
       <c r="B42" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>157355.30980000002</v>
       </c>
-      <c r="D42" s="4"/>
       <c r="E42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,12 +1895,11 @@
       <c r="B43" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>50851.812500000029</v>
       </c>
-      <c r="D43" s="4"/>
       <c r="E43" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,12 +1909,11 @@
       <c r="B44" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>131106.02059999996</v>
       </c>
-      <c r="D44" s="4"/>
       <c r="E44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,87 +1923,81 @@
       <c r="B45" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>14998.798000000006</v>
       </c>
-      <c r="D45" s="4"/>
       <c r="E45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>53282.281299999988</v>
       </c>
-      <c r="D46" s="4"/>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
-      </c>
-      <c r="C47" s="7">
+        <v>142</v>
+      </c>
+      <c r="C47" s="6">
         <v>2291038214.1599998</v>
       </c>
-      <c r="D47" s="4"/>
       <c r="E47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
-      </c>
-      <c r="C48" s="7">
+        <v>163</v>
+      </c>
+      <c r="C48" s="6">
         <v>18270901.850000001</v>
       </c>
-      <c r="D48" s="4"/>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>174</v>
-      </c>
-      <c r="C49" s="7">
+        <v>172</v>
+      </c>
+      <c r="C49" s="6">
         <v>5350.34</v>
       </c>
-      <c r="D49" s="4"/>
       <c r="E49" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
-      </c>
-      <c r="C50" s="8">
+        <v>136</v>
+      </c>
+      <c r="C50" s="7">
         <v>543306877.47000003</v>
       </c>
-      <c r="D50" s="4"/>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2064,12 +2007,11 @@
       <c r="B51" t="s">
         <v>50</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>4646496137.2200003</v>
       </c>
-      <c r="D51" s="4"/>
       <c r="E51" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2079,582 +2021,543 @@
       <c r="B52" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>866391462.78999996</v>
       </c>
-      <c r="D52" s="4"/>
       <c r="E52" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B53" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>3625807.5199999996</v>
       </c>
-      <c r="D53" s="4"/>
       <c r="E53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <v>299551.90000000002</v>
       </c>
-      <c r="D54" s="4"/>
       <c r="E54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C55" s="10">
+        <v>112</v>
+      </c>
+      <c r="C55" s="9">
         <v>14865567.58</v>
       </c>
-      <c r="D55" s="4"/>
       <c r="E55" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B56" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="9">
         <v>299781.48</v>
       </c>
-      <c r="D56" s="4"/>
       <c r="E56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="9">
         <v>68528.479999999996</v>
       </c>
-      <c r="D57" s="4"/>
       <c r="E57" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B58" t="s">
         <v>57</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="9">
         <v>241113.19999999998</v>
       </c>
-      <c r="D58" s="4"/>
       <c r="E58" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="10">
+        <v>117</v>
+      </c>
+      <c r="C59" s="9">
         <v>1164343.07</v>
       </c>
-      <c r="D59" s="4"/>
       <c r="E59" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B60" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="9">
         <v>114846.95999999999</v>
       </c>
-      <c r="D60" s="4"/>
       <c r="E60" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="9">
         <v>64403.810000000005</v>
       </c>
-      <c r="D61" s="4"/>
       <c r="E61" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B62" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="9">
         <v>19768.719999999998</v>
       </c>
-      <c r="D62" s="4"/>
       <c r="E62" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
         <v>65</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="9">
         <v>5748949.5499999998</v>
       </c>
-      <c r="D63" s="4"/>
       <c r="E63" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
         <v>59</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="9">
         <v>2699171.33</v>
       </c>
-      <c r="D64" s="4"/>
       <c r="E64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
         <v>60</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="9">
         <v>695047.14</v>
       </c>
-      <c r="D65" s="4"/>
       <c r="E65" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
         <v>61</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="9">
         <v>933808.6</v>
       </c>
-      <c r="D66" s="4"/>
       <c r="E66" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B67" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="9">
         <v>1232297.5</v>
       </c>
-      <c r="D67" s="4"/>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="10">
         <v>134265.85</v>
       </c>
-      <c r="D68" s="4"/>
       <c r="E68" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <v>263872791.57080001</v>
       </c>
-      <c r="D69" s="13"/>
       <c r="E69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="11">
         <v>2847814.72</v>
       </c>
-      <c r="D70" s="13"/>
       <c r="E70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="11">
         <v>12029713.060000001</v>
       </c>
-      <c r="D71" s="13"/>
       <c r="E71" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="11">
         <v>48486.37</v>
       </c>
-      <c r="D72" s="13"/>
       <c r="E72" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="11">
         <v>43112.88</v>
       </c>
-      <c r="D73" s="13"/>
       <c r="E73" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="11">
         <v>923983.56</v>
       </c>
-      <c r="D74" s="13"/>
       <c r="E74" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="11">
         <v>2570027.67</v>
       </c>
-      <c r="D75" s="13"/>
       <c r="E75" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="11">
         <v>2414101.79</v>
       </c>
-      <c r="D76" s="13"/>
       <c r="E76" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="11">
         <v>503679.39</v>
       </c>
-      <c r="D77" s="13"/>
       <c r="E77" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="11">
         <v>380826.56</v>
       </c>
-      <c r="D78" s="13"/>
       <c r="E78" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="11">
         <v>357284.66</v>
       </c>
-      <c r="D79" s="13"/>
       <c r="E79" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="80" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C80" s="12">
+        <v>165</v>
+      </c>
+      <c r="C80" s="11">
         <v>1063053.51</v>
       </c>
-      <c r="D80" s="13"/>
       <c r="E80" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14">
+      <c r="D81" s="1">
         <v>2749018.95</v>
       </c>
       <c r="E81" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14">
+      <c r="D82" s="1">
         <v>471856.2</v>
       </c>
       <c r="E82" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
-      </c>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14">
-        <v>12304.12</v>
+        <v>79</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2271099.38</v>
       </c>
       <c r="E83" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14">
-        <v>2271099.38</v>
+        <v>128</v>
+      </c>
+      <c r="D84" s="1">
+        <v>67710140.400000006</v>
       </c>
       <c r="E84" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14">
-        <v>67710140.400000006</v>
+        <v>129</v>
+      </c>
+      <c r="D85" s="1">
+        <v>3217616.75</v>
       </c>
       <c r="E85" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B86" t="s">
-        <v>131</v>
-      </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14">
-        <v>3217616.75</v>
+        <v>130</v>
+      </c>
+      <c r="D86" s="1">
+        <v>5745663.5460000001</v>
       </c>
       <c r="E86" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
-      </c>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14">
-        <v>5745663.5460000001</v>
+        <v>131</v>
+      </c>
+      <c r="D87" s="1">
+        <v>5641544.9900000002</v>
       </c>
       <c r="E87" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="B88" t="s">
-        <v>133</v>
-      </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14">
-        <v>5641544.9900000002</v>
+        <v>76</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5303264.82</v>
       </c>
       <c r="E88" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="14"/>
-      <c r="D89" s="14">
-        <v>5303264.82</v>
+        <v>78</v>
+      </c>
+      <c r="D89" s="1">
+        <v>215.29</v>
       </c>
       <c r="E89" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
-      </c>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14">
-        <v>215.29</v>
+        <v>192</v>
+      </c>
+      <c r="D90" s="1">
+        <v>38308.49</v>
       </c>
       <c r="E90" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2664,12 +2567,11 @@
       <c r="B91" t="s">
         <v>194</v>
       </c>
-      <c r="C91" s="14"/>
-      <c r="D91" s="14">
-        <v>38308.49</v>
+      <c r="D91" s="1">
+        <v>1208.48</v>
       </c>
       <c r="E91" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2677,29 +2579,27 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
-      </c>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14">
-        <v>1208.48</v>
+        <v>177</v>
+      </c>
+      <c r="D92" s="1">
+        <v>14.91</v>
       </c>
       <c r="E92" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" t="s">
         <v>197</v>
       </c>
-      <c r="B93" t="s">
-        <v>179</v>
-      </c>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14">
-        <v>14.91</v>
+      <c r="D93" s="1">
+        <v>608.48</v>
       </c>
       <c r="E93" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2709,12 +2609,11 @@
       <c r="B94" t="s">
         <v>199</v>
       </c>
-      <c r="C94" s="14"/>
-      <c r="D94" s="14">
-        <v>608.48</v>
+      <c r="D94" s="1">
+        <v>99402402.335999995</v>
       </c>
       <c r="E94" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2724,42 +2623,40 @@
       <c r="B95" t="s">
         <v>201</v>
       </c>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14">
-        <v>99402402.335999995</v>
+      <c r="D95" s="1">
+        <v>3012689.14</v>
       </c>
       <c r="E95" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14">
-        <v>3012689.14</v>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11">
+        <v>133.26595687866211</v>
       </c>
       <c r="E96" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>204</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" t="s">
         <v>205</v>
       </c>
-      <c r="C97" s="12"/>
-      <c r="D97" s="12">
-        <v>133.26595687866211</v>
+      <c r="D97" s="1">
+        <v>1567.41</v>
       </c>
       <c r="E97" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2769,12 +2666,11 @@
       <c r="B98" t="s">
         <v>207</v>
       </c>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14">
-        <v>1567.41</v>
+      <c r="D98" s="1">
+        <v>2145973.2799999998</v>
       </c>
       <c r="E98" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2784,12 +2680,11 @@
       <c r="B99" t="s">
         <v>209</v>
       </c>
-      <c r="C99" s="14"/>
-      <c r="D99" s="14">
-        <v>2145973.2799999998</v>
+      <c r="D99" s="1">
+        <v>14001240.210000001</v>
       </c>
       <c r="E99" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2799,12 +2694,11 @@
       <c r="B100" t="s">
         <v>211</v>
       </c>
-      <c r="C100" s="14"/>
-      <c r="D100" s="14">
-        <v>14001240.210000001</v>
+      <c r="D100" s="1">
+        <v>155430993.75</v>
       </c>
       <c r="E100" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2812,29 +2706,27 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>213</v>
-      </c>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14">
-        <v>155430993.75</v>
+        <v>266</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1865107.09</v>
       </c>
       <c r="E101" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>213</v>
+      </c>
+      <c r="B102" t="s">
         <v>214</v>
       </c>
-      <c r="B102" t="s">
-        <v>268</v>
-      </c>
-      <c r="C102" s="14"/>
-      <c r="D102" s="14">
-        <v>1865107.09</v>
+      <c r="D102" s="1">
+        <v>1861975.33</v>
       </c>
       <c r="E102" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2844,12 +2736,11 @@
       <c r="B103" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14">
-        <v>1861975.33</v>
+      <c r="D103" s="1">
+        <v>18418949.199999999</v>
       </c>
       <c r="E103" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2859,12 +2750,11 @@
       <c r="B104" t="s">
         <v>218</v>
       </c>
-      <c r="C104" s="14"/>
-      <c r="D104" s="14">
-        <v>18418949.199999999</v>
+      <c r="D104" s="1">
+        <v>310715.68</v>
       </c>
       <c r="E104" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2874,12 +2764,11 @@
       <c r="B105" t="s">
         <v>220</v>
       </c>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14">
-        <v>310715.68</v>
+      <c r="D105" s="1">
+        <v>26116.92</v>
       </c>
       <c r="E105" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2889,12 +2778,11 @@
       <c r="B106" t="s">
         <v>222</v>
       </c>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14">
-        <v>26116.92</v>
+      <c r="D106" s="1">
+        <v>317421.90000000002</v>
       </c>
       <c r="E106" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2904,12 +2792,11 @@
       <c r="B107" t="s">
         <v>224</v>
       </c>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14">
-        <v>317421.90000000002</v>
+      <c r="D107" s="1">
+        <v>301481.4852</v>
       </c>
       <c r="E107" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2919,12 +2806,11 @@
       <c r="B108" t="s">
         <v>226</v>
       </c>
-      <c r="C108" s="14"/>
-      <c r="D108" s="14">
-        <v>301481.4852</v>
+      <c r="D108" s="1">
+        <v>1129551.26</v>
       </c>
       <c r="E108" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -2934,12 +2820,11 @@
       <c r="B109" t="s">
         <v>228</v>
       </c>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14">
-        <v>1129551.26</v>
+      <c r="D109" s="1">
+        <v>2333633.69</v>
       </c>
       <c r="E109" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -2949,12 +2834,11 @@
       <c r="B110" t="s">
         <v>230</v>
       </c>
-      <c r="C110" s="14"/>
-      <c r="D110" s="14">
-        <v>2333633.69</v>
+      <c r="D110" s="1">
+        <v>179849700.68000001</v>
       </c>
       <c r="E110" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -2964,12 +2848,11 @@
       <c r="B111" t="s">
         <v>232</v>
       </c>
-      <c r="C111" s="14"/>
-      <c r="D111" s="14">
-        <v>179849700.68000001</v>
+      <c r="D111" s="1">
+        <v>11832158.699999999</v>
       </c>
       <c r="E111" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -2979,12 +2862,11 @@
       <c r="B112" t="s">
         <v>234</v>
       </c>
-      <c r="C112" s="14"/>
-      <c r="D112" s="14">
-        <v>11832158.699999999</v>
+      <c r="D112" s="1">
+        <v>7478564.6600000001</v>
       </c>
       <c r="E112" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2994,12 +2876,11 @@
       <c r="B113" t="s">
         <v>236</v>
       </c>
-      <c r="C113" s="14"/>
-      <c r="D113" s="14">
-        <v>7478564.6600000001</v>
+      <c r="D113" s="1">
+        <v>211368.76</v>
       </c>
       <c r="E113" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -3007,29 +2888,27 @@
         <v>237</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
-      </c>
-      <c r="C114" s="14"/>
-      <c r="D114" s="14">
-        <v>211368.76</v>
+        <v>37</v>
+      </c>
+      <c r="D114" s="1">
+        <v>4135424</v>
       </c>
       <c r="E114" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>238</v>
+      </c>
+      <c r="B115" t="s">
         <v>239</v>
       </c>
-      <c r="B115" t="s">
-        <v>37</v>
-      </c>
-      <c r="C115" s="14"/>
-      <c r="D115" s="14">
-        <v>4135424</v>
+      <c r="D115" s="1">
+        <v>930116.55</v>
       </c>
       <c r="E115" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -3039,12 +2918,11 @@
       <c r="B116" t="s">
         <v>241</v>
       </c>
-      <c r="C116" s="14"/>
-      <c r="D116" s="14">
-        <v>930116.55</v>
+      <c r="D116" s="1">
+        <v>160690.60999999999</v>
       </c>
       <c r="E116" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -3054,12 +2932,11 @@
       <c r="B117" t="s">
         <v>243</v>
       </c>
-      <c r="C117" s="14"/>
-      <c r="D117" s="14">
-        <v>160690.60999999999</v>
+      <c r="D117" s="1">
+        <v>6304464293.5200005</v>
       </c>
       <c r="E117" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -3069,12 +2946,11 @@
       <c r="B118" t="s">
         <v>245</v>
       </c>
-      <c r="C118" s="14"/>
-      <c r="D118" s="14">
-        <v>6304464293.5200005</v>
+      <c r="D118" s="1">
+        <v>5824449.4800000004</v>
       </c>
       <c r="E118" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -3084,12 +2960,11 @@
       <c r="B119" t="s">
         <v>247</v>
       </c>
-      <c r="C119" s="14"/>
-      <c r="D119" s="14">
-        <v>5824449.4800000004</v>
+      <c r="D119" s="1">
+        <v>175684.91</v>
       </c>
       <c r="E119" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -3099,12 +2974,11 @@
       <c r="B120" t="s">
         <v>249</v>
       </c>
-      <c r="C120" s="14"/>
-      <c r="D120" s="14">
-        <v>175684.91</v>
+      <c r="D120" s="1">
+        <v>869752.98</v>
       </c>
       <c r="E120" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -3114,12 +2988,11 @@
       <c r="B121" t="s">
         <v>251</v>
       </c>
-      <c r="C121" s="14"/>
-      <c r="D121" s="14">
-        <v>869752.98</v>
+      <c r="D121" s="1">
+        <v>280.72000000000003</v>
       </c>
       <c r="E121" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -3129,12 +3002,11 @@
       <c r="B122" t="s">
         <v>253</v>
       </c>
-      <c r="C122" s="14"/>
-      <c r="D122" s="14">
-        <v>280.72000000000003</v>
+      <c r="D122" s="1">
+        <v>327.18</v>
       </c>
       <c r="E122" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3144,57 +3016,53 @@
       <c r="B123" t="s">
         <v>255</v>
       </c>
-      <c r="C123" s="14"/>
-      <c r="D123" s="14">
-        <v>327.18</v>
+      <c r="D123" s="1">
+        <v>108828198.84999999</v>
       </c>
       <c r="E123" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" t="s">
         <v>256</v>
       </c>
-      <c r="B124" t="s">
-        <v>257</v>
-      </c>
-      <c r="C124" s="14"/>
-      <c r="D124" s="14">
-        <v>108828198.84999999</v>
+      <c r="D124" s="1">
+        <v>188172.57</v>
       </c>
       <c r="E124" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>269</v>
+        <v>38</v>
       </c>
       <c r="B125" t="s">
-        <v>258</v>
-      </c>
-      <c r="C125" s="14"/>
-      <c r="D125" s="14">
-        <v>188172.57</v>
+        <v>37</v>
+      </c>
+      <c r="D125" s="1">
+        <v>14656419.369999999</v>
       </c>
       <c r="E125" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="B126" t="s">
-        <v>37</v>
-      </c>
-      <c r="C126" s="14"/>
-      <c r="D126" s="14">
-        <v>14656419.369999999</v>
+        <v>258</v>
+      </c>
+      <c r="D126" s="1">
+        <v>2436847.61</v>
       </c>
       <c r="E126" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3204,12 +3072,11 @@
       <c r="B127" t="s">
         <v>260</v>
       </c>
-      <c r="C127" s="14"/>
-      <c r="D127" s="14">
-        <v>2436847.61</v>
+      <c r="D127" s="1">
+        <v>210408370.97</v>
       </c>
       <c r="E127" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3219,12 +3086,11 @@
       <c r="B128" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="14"/>
-      <c r="D128" s="14">
-        <v>210408370.97</v>
+      <c r="D128" s="1">
+        <v>119399284.58</v>
       </c>
       <c r="E128" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3234,27 +3100,25 @@
       <c r="B129" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="14"/>
-      <c r="D129" s="14">
-        <v>119399284.58</v>
+      <c r="D129" s="1">
+        <v>18270901.850000001</v>
       </c>
       <c r="E129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="B130" t="s">
-        <v>266</v>
-      </c>
-      <c r="C130" s="14"/>
-      <c r="D130" s="14">
-        <v>18270901.850000001</v>
+        <v>183</v>
+      </c>
+      <c r="D130" s="1">
+        <v>5724713974.3900003</v>
       </c>
       <c r="E130" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3262,134 +3126,112 @@
         <v>184</v>
       </c>
       <c r="B131" t="s">
-        <v>185</v>
-      </c>
-      <c r="C131" s="14"/>
-      <c r="D131" s="14">
-        <v>5724713974.3900003</v>
+        <v>186</v>
+      </c>
+      <c r="D131" s="1">
+        <v>254045481</v>
       </c>
       <c r="E131" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B132" t="s">
-        <v>188</v>
-      </c>
-      <c r="C132" s="14"/>
-      <c r="D132" s="14">
-        <v>254045481</v>
+        <v>187</v>
+      </c>
+      <c r="D132" s="1">
+        <v>357161.62</v>
       </c>
       <c r="E132" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B133" t="s">
-        <v>189</v>
-      </c>
-      <c r="C133" s="14"/>
-      <c r="D133" s="14">
-        <v>357161.62</v>
+        <v>190</v>
+      </c>
+      <c r="D133" s="1">
+        <v>893049.75</v>
       </c>
       <c r="E133" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>190</v>
-      </c>
-      <c r="B134" t="s">
-        <v>192</v>
-      </c>
-      <c r="C134" s="14"/>
-      <c r="D134" s="14">
-        <v>893049.75</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11">
+        <v>299459436.56529999</v>
       </c>
       <c r="E134" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12">
-        <v>299459436.56529999</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>72</v>
+      </c>
+      <c r="B135" t="s">
+        <v>50</v>
+      </c>
+      <c r="D135" s="1">
+        <v>4383811320.8699999</v>
       </c>
       <c r="E135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
-      </c>
-      <c r="C136" s="14"/>
-      <c r="D136" s="14">
-        <v>4383811320.8699999</v>
+        <v>51</v>
+      </c>
+      <c r="D136" s="1">
+        <v>791380414.20000005</v>
       </c>
       <c r="E136" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B137" t="s">
-        <v>51</v>
-      </c>
-      <c r="C137" s="14"/>
-      <c r="D137" s="14">
-        <v>791380414.20000005</v>
+        <v>52</v>
+      </c>
+      <c r="D137" s="1">
+        <v>38199.89</v>
       </c>
       <c r="E137" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>52</v>
-      </c>
-      <c r="C138" s="14"/>
-      <c r="D138" s="14">
-        <v>38199.89</v>
+        <v>180</v>
+      </c>
+      <c r="D138" s="1">
+        <v>635531212.66999996</v>
       </c>
       <c r="E138" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>191</v>
-      </c>
-      <c r="B139" t="s">
-        <v>182</v>
-      </c>
-      <c r="C139" s="14"/>
-      <c r="D139" s="14">
-        <v>635531212.66999996</v>
-      </c>
-      <c r="E139" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/public/PresupuestoInicial/Poliza Inicial v2.xlsx
+++ b/public/PresupuestoInicial/Poliza Inicial v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SAC-IPE\public\PresupuestoInicial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C446ADD-711D-4A31-B171-39728BC7A075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91BFEA5-1E9A-4827-9324-1531821E4283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" xr2:uid="{1ABF5C7F-72DD-4BD5-835F-CAF0BF8EAFC5}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="840" xr2:uid="{1ABF5C7F-72DD-4BD5-835F-CAF0BF8EAFC5}"/>
   </bookViews>
   <sheets>
     <sheet name="POLIZA PRUEBA TECNOLOGIAS" sheetId="17" r:id="rId1"/>
@@ -1336,7 +1336,7 @@
         <v>85</v>
       </c>
       <c r="C3" s="3">
-        <v>5030912.280000153</v>
+        <v>5030912.28</v>
       </c>
       <c r="E3" t="s">
         <v>139</v>
@@ -1420,7 +1420,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="3">
-        <v>4789717.675999999</v>
+        <v>4789717.67</v>
       </c>
       <c r="E9" t="s">
         <v>139</v>
@@ -1462,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="3">
-        <v>7259171.2219999693</v>
+        <v>7259171.2199999997</v>
       </c>
       <c r="E12" t="s">
         <v>139</v>
@@ -1602,7 +1602,7 @@
         <v>145</v>
       </c>
       <c r="C22" s="4">
-        <v>12067744.582</v>
+        <v>12067744.58</v>
       </c>
       <c r="E22" t="s">
         <v>139</v>
@@ -1742,7 +1742,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="4">
-        <v>265818246.87500003</v>
+        <v>265818246.87</v>
       </c>
       <c r="E32" t="s">
         <v>139</v>
@@ -1756,7 +1756,7 @@
         <v>20</v>
       </c>
       <c r="C33" s="5">
-        <v>615911.88406816381</v>
+        <v>615911.88</v>
       </c>
       <c r="E33" t="s">
         <v>139</v>
@@ -1770,7 +1770,7 @@
         <v>21</v>
       </c>
       <c r="C34" s="5">
-        <v>2556343.3448425638</v>
+        <v>2556343.34</v>
       </c>
       <c r="E34" t="s">
         <v>139</v>
@@ -1784,7 +1784,7 @@
         <v>23</v>
       </c>
       <c r="C35" s="5">
-        <v>34801.649000000012</v>
+        <v>34801.64</v>
       </c>
       <c r="E35" t="s">
         <v>139</v>
@@ -1798,7 +1798,7 @@
         <v>25</v>
       </c>
       <c r="C36" s="5">
-        <v>1059043.9312546314</v>
+        <v>1059043.93</v>
       </c>
       <c r="E36" t="s">
         <v>139</v>
@@ -1826,7 +1826,7 @@
         <v>27</v>
       </c>
       <c r="C38" s="5">
-        <v>98906.146800000002</v>
+        <v>98906.14</v>
       </c>
       <c r="E38" t="s">
         <v>139</v>
@@ -1840,7 +1840,7 @@
         <v>28</v>
       </c>
       <c r="C39" s="5">
-        <v>1211367.5394236788</v>
+        <v>1211367.53</v>
       </c>
       <c r="E39" t="s">
         <v>139</v>
@@ -1854,7 +1854,7 @@
         <v>29</v>
       </c>
       <c r="C40" s="5">
-        <v>1027144.490864502</v>
+        <v>1027144.49</v>
       </c>
       <c r="E40" t="s">
         <v>139</v>
@@ -1868,7 +1868,7 @@
         <v>30</v>
       </c>
       <c r="C41" s="5">
-        <v>181504.81520000001</v>
+        <v>181504.81</v>
       </c>
       <c r="E41" t="s">
         <v>139</v>
@@ -1882,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>157355.30980000002</v>
+        <v>157355.29999999999</v>
       </c>
       <c r="E42" t="s">
         <v>139</v>
@@ -1896,7 +1896,7 @@
         <v>32</v>
       </c>
       <c r="C43" s="5">
-        <v>50851.812500000029</v>
+        <v>50851.81</v>
       </c>
       <c r="E43" t="s">
         <v>139</v>
@@ -1910,7 +1910,7 @@
         <v>33</v>
       </c>
       <c r="C44" s="5">
-        <v>131106.02059999996</v>
+        <v>131106.01999999999</v>
       </c>
       <c r="E44" t="s">
         <v>139</v>
@@ -1924,7 +1924,7 @@
         <v>34</v>
       </c>
       <c r="C45" s="5">
-        <v>14998.798000000006</v>
+        <v>14998.79</v>
       </c>
       <c r="E45" t="s">
         <v>139</v>
@@ -1938,7 +1938,7 @@
         <v>35</v>
       </c>
       <c r="C46" s="5">
-        <v>53282.281299999988</v>
+        <v>53282.28</v>
       </c>
       <c r="E46" t="s">
         <v>139</v>
@@ -2260,7 +2260,7 @@
         <v>51</v>
       </c>
       <c r="C69" s="11">
-        <v>263872791.57080001</v>
+        <v>263872791.56999999</v>
       </c>
       <c r="E69" t="s">
         <v>140</v>
@@ -2498,7 +2498,7 @@
         <v>130</v>
       </c>
       <c r="D86" s="1">
-        <v>5745663.5460000001</v>
+        <v>5745663.54</v>
       </c>
       <c r="E86" t="s">
         <v>140</v>
@@ -2610,7 +2610,7 @@
         <v>199</v>
       </c>
       <c r="D94" s="1">
-        <v>99402402.335999995</v>
+        <v>99402402.329999998</v>
       </c>
       <c r="E94" t="s">
         <v>140</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11">
-        <v>133.26595687866211</v>
+        <v>133.26</v>
       </c>
       <c r="E96" t="s">
         <v>140</v>
@@ -2793,7 +2793,7 @@
         <v>224</v>
       </c>
       <c r="D107" s="1">
-        <v>301481.4852</v>
+        <v>301481.48</v>
       </c>
       <c r="E107" t="s">
         <v>140</v>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11">
-        <v>299459436.56529999</v>
+        <v>299459436.56</v>
       </c>
       <c r="E134" t="s">
         <v>139</v>
